--- a/salon_forms/012_wax_room_check_in_form_template--salon_forms.xlsx
+++ b/salon_forms/012_wax_room_check_in_form_template--salon_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Client's Date of Visit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>technician_name</t>
+          <t>client_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Technician Name</t>
+          <t>Client Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>client_name</t>
+          <t>equipment_condition</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Client Name</t>
+          <t>Equipment Condition</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>equipment_condition</t>
+          <t>chemicals_condition</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Equipment Condition</t>
+          <t>Chemicals Condition</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>chemicals_condition</t>
+          <t>wax_condition</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chemicals Condition</t>
+          <t>Wax Condition</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>wax_condition</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wax Condition</t>
+          <t>Additional Notes</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,40 +653,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>technician_signature</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Technician's Signature</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>signature</t>
+          <t>yes_no_equipment_condition</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Technician Signature</t>
+          <t>Equipment Condition (Yes/No)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>equipment_condition_3</t>
+          <t>chemicals_condition_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Equipment Condition</t>
+          <t>Chemicals Condition 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>chemicals_condition_3</t>
+          <t>technician_name</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chemicals Condition</t>
+          <t>Technician's Name</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,40 +745,40 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>technician_name</t>
+          <t>additional_notes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Technician Name</t>
+          <t>Additional Notes (2)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>notes_2</t>
+          <t>yes_no_equipment_condition_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Yes No Equipment Condition 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,16 +796,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>equipment_condition_5</t>
+          <t>chemicals_condition_2_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Equipment Condition</t>
+          <t>Chemicals Condition 2 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>notes_2</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -822,10 +845,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1037,41 +1060,41 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>equipment_condition_3_choices</t>
+          <t>yes_no_equipment_condition_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>equipment_condition_3_choices</t>
+          <t>yes_no_equipment_condition_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>chemicals_condition_3_choices</t>
+          <t>chemicals_condition_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1088,7 +1111,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>chemicals_condition_3_choices</t>
+          <t>chemicals_condition_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1105,7 +1128,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>chemicals_condition_3_choices</t>
+          <t>chemicals_condition_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1122,34 +1145,85 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>equipment_condition_5_choices</t>
+          <t>yes_no_equipment_condition_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>equipment_condition_5_choices</t>
+          <t>yes_no_equipment_condition_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>chemicals_condition_2_2_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>chemicals_condition_2_2_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>chemicals_condition_2_2_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
